--- a/data/hex_xlsx/TNOM.HE.xlsx
+++ b/data/hex_xlsx/TNOM.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="295">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -558,22 +558,25 @@
     <t>Total Long Term Debt &amp; Lease</t>
   </si>
   <si>
+    <t>Financial liabilities LT</t>
+  </si>
+  <si>
+    <t>Trade and other payables</t>
+  </si>
+  <si>
+    <t>Non-current Liabilities - Total</t>
+  </si>
+  <si>
+    <t>Deferred tax liabilities</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Liabilities</t>
+  </si>
+  <si>
+    <t>Total Non-current Liabilities</t>
+  </si>
+  <si>
     <t>Financial liabilities</t>
-  </si>
-  <si>
-    <t>Trade and other payables</t>
-  </si>
-  <si>
-    <t>Non-current Liabilities - Total</t>
-  </si>
-  <si>
-    <t>Deferred tax liabilities</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Liabilities</t>
-  </si>
-  <si>
-    <t>Total Non-current Liabilities</t>
   </si>
   <si>
     <t>Other Current Liabilities - Total</t>
@@ -1032,7 +1035,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1110,6 +1113,12 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -6832,7 +6841,7 @@
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="26" t="s">
         <v>179</v>
       </c>
       <c r="B73" s="15">
@@ -7059,7 +7068,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B80" s="20">
         <v>5.32</v>
@@ -7073,9 +7082,15 @@
       <c r="E80" s="15">
         <v>104.85</v>
       </c>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
+      <c r="F80" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="G80" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="H80" s="27">
+        <v>0.0</v>
+      </c>
       <c r="I80" s="19">
         <v>0.0</v>
       </c>
@@ -7159,7 +7174,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
@@ -7183,7 +7198,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="20">
         <v>42.87</v>
@@ -7201,7 +7216,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B85" s="20">
         <v>0.8</v>
@@ -7239,7 +7254,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -7261,7 +7276,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B87" s="17">
         <v>341.33</v>
@@ -7299,7 +7314,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
@@ -7321,7 +7336,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B89" s="17">
         <v>1573.5</v>
@@ -7359,7 +7374,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
@@ -7385,7 +7400,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B91" s="17">
         <v>2129.18</v>
@@ -7423,7 +7438,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B92" s="20">
         <v>0.15</v>
@@ -7461,7 +7476,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B93" s="20">
         <v>45.48</v>
@@ -7499,7 +7514,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B94" s="20">
         <v>45.63</v>
@@ -7537,7 +7552,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B95" s="20">
         <v>45.63</v>
@@ -7575,7 +7590,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B96" s="20">
         <v>45.48</v>
@@ -7613,7 +7628,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B97" s="20">
         <v>0.15</v>
@@ -7651,7 +7666,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B98" s="20">
         <v>1.0</v>
@@ -8611,7 +8626,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8854,37 +8869,37 @@
         <v>33</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -8927,7 +8942,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -9095,7 +9110,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B23" s="20">
         <v>47.54</v>
@@ -9133,7 +9148,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" s="20">
         <v>1.8</v>
@@ -9151,7 +9166,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B25" s="20">
         <v>17.94</v>
@@ -9189,7 +9204,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B26" s="18">
         <v>-25.51</v>
@@ -9227,7 +9242,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B27" s="20">
         <v>4.41</v>
@@ -9265,7 +9280,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="20">
         <v>2.42</v>
@@ -9303,7 +9318,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B29" s="18">
         <v>-14.59</v>
@@ -9341,7 +9356,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B30" s="20">
         <v>0.01</v>
@@ -9367,7 +9382,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B31" s="17">
         <v>371.02</v>
@@ -9405,7 +9420,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B32" s="20">
         <v>3.04</v>
@@ -9443,7 +9458,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B33" s="18">
         <v>-19.91</v>
@@ -9481,7 +9496,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B34" s="18">
         <v>-42.11</v>
@@ -9519,7 +9534,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B35" s="25">
         <v>-136.31</v>
@@ -9557,7 +9572,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B36" s="18">
         <v>-47.42</v>
@@ -9593,7 +9608,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20">
@@ -9617,7 +9632,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B38" s="18">
         <v>-0.27</v>
@@ -9645,27 +9660,27 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" s="26">
+        <v>221</v>
+      </c>
+      <c r="B39" s="28">
         <v>-242.97</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="28">
         <v>-267.76</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="28">
         <v>-389.68</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="28">
         <v>-322.8</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="28">
         <v>-247.76</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="28">
         <v>-188.33</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="28">
         <v>-128.91</v>
       </c>
       <c r="I39" s="23">
@@ -9683,7 +9698,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="19">
@@ -9711,7 +9726,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -9733,7 +9748,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -9755,7 +9770,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B43" s="18">
         <v>-45.17</v>
@@ -9793,7 +9808,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B44" s="25">
         <v>-106.45</v>
@@ -9831,7 +9846,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B45" s="20">
         <v>58.51</v>
@@ -9867,7 +9882,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B46" s="18">
         <v>-0.68</v>
@@ -9903,7 +9918,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B47" s="18">
         <v>-1.6</v>
@@ -9941,7 +9956,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B48" s="18">
         <v>-46.45</v>
@@ -9971,7 +9986,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -9995,9 +10010,9 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" s="26">
+        <v>232</v>
+      </c>
+      <c r="B50" s="28">
         <v>-141.84</v>
       </c>
       <c r="C50" s="23">
@@ -10033,7 +10048,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B51" s="18">
         <v>-5.18</v>
@@ -10051,7 +10066,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B52" s="23">
         <v>-5.18</v>
@@ -10069,7 +10084,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" s="15">
         <v>102.42</v>
@@ -10107,7 +10122,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" s="20">
         <v>82.76</v>
@@ -10145,7 +10160,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B55" s="18">
         <v>-0.49</v>
@@ -10173,7 +10188,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B56" s="18">
         <v>-13.79</v>
@@ -10201,7 +10216,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -10219,7 +10234,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B58" s="23">
         <v>-19.46</v>
@@ -11219,7 +11234,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11341,10 +11356,10 @@
         <v>28</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -11554,7 +11569,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -11604,1401 +11619,1401 @@
         <v>48</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
+      <c r="A20" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="32">
         <v>2490.01</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="32">
         <v>2956.63</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="32">
         <v>3436.05</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="32">
         <v>5518.96</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="32">
         <v>7117.7</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="32">
         <v>3370.19</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="32">
         <v>1471.24</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="32">
         <v>1009.72</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="32">
         <v>589.44</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="32">
         <v>501.99</v>
       </c>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B22" s="32">
         <v>4787.65</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="32">
         <v>4843.64</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="32">
         <v>4297.27</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="32">
         <v>3652.62</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="32">
         <v>2803.15</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="32">
         <v>1398.82</v>
       </c>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
+      <c r="A23" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" s="32">
         <v>1459.02</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="32">
         <v>2115.51</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="32">
         <v>2868.7</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="32">
         <v>5129.34</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="32">
         <v>6813.53</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="32">
         <v>3087.69</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="32">
         <v>1297.01</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="32">
         <v>836.24</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="32">
         <v>424.47</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="32">
         <v>327.86</v>
       </c>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="32">
         <v>4117.21</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="32">
         <v>4338.13</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="32">
         <v>3944.24</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="32">
         <v>3388.58</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="32">
         <v>2570.33</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="32">
         <v>1201.57</v>
       </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
+      <c r="A26" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="34">
         <v>31.98</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="34">
         <v>46.42</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <v>63.86</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="32">
         <v>117.13</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="32">
         <v>157.67</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="34">
         <v>73.8</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="34">
         <v>31.46</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="34">
         <v>20.46</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="34">
         <v>10.39</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="34">
         <v>8.02</v>
       </c>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="34">
         <v>72.63</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="34">
         <v>74.19</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="34">
         <v>65.3</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="34">
         <v>79.1</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="34">
         <v>60.65</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="34">
         <v>29.0</v>
       </c>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
+      <c r="A29" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="35">
         <v>6.44</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="35">
         <v>4.15</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="35">
         <v>4.96</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="35">
         <v>2.35</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="35">
         <v>1.75</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="35">
         <v>3.32</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="35">
         <v>4.97</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="35">
         <v>5.4</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="35">
         <v>4.71</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="36">
         <v>-7.52</v>
       </c>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="35">
         <v>3.85</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="35">
         <v>3.8</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="35">
         <v>4.0</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="35">
         <v>2.68</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="35">
         <v>2.89</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="35">
         <v>3.46</v>
       </c>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="A32" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="35">
         <v>6.99</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="35">
         <v>4.34</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="35">
         <v>2.79</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="35">
         <v>1.28</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="35">
         <v>4.98</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="35">
         <v>1.22</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="35">
         <v>0.0</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="35">
         <v>0.0</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="35">
         <v>0.0</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="35">
         <v>0.0</v>
       </c>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="35">
         <v>4.67</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="35">
         <v>4.05</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="35">
         <v>3.73</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="35">
         <v>2.51</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="35">
         <v>2.91</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="35">
         <v>0.62</v>
       </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="35">
         <v>6.99</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="35">
         <v>4.34</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="35">
         <v>2.79</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="35">
         <v>1.28</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="35">
         <v>4.98</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="35">
         <v>1.22</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="35">
         <v>0.0</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="35">
         <v>0.0</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="35">
         <v>0.0</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="35">
         <v>0.0</v>
       </c>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="35">
         <v>4.67</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="35">
         <v>4.05</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="35">
         <v>3.73</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="35">
         <v>2.51</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="35">
         <v>2.91</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="35">
         <v>0.62</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
+      <c r="A37" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="34">
         <v>2.27</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="34">
         <v>3.38</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="34">
         <v>4.87</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="34">
         <v>11.42</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="34">
         <v>20.15</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="34">
         <v>13.26</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="34">
         <v>7.0</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="34">
         <v>6.09</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="34">
         <v>3.99</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="34">
         <v>3.64</v>
       </c>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="B39" s="34">
         <v>5.67</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="34">
         <v>6.88</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="34">
         <v>7.7</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="34">
         <v>12.61</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="34">
         <v>12.09</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="34">
         <v>7.85</v>
       </c>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
+      <c r="A40" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="34">
         <v>0.98</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="34">
         <v>1.54</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="34">
         <v>2.65</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="34">
         <v>6.16</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="34">
         <v>9.98</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="34">
         <v>5.59</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="34">
         <v>2.74</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="34">
         <v>2.09</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="34">
         <v>1.26</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="34">
         <v>1.03</v>
       </c>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="B42" s="34">
         <v>2.76</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="34">
         <v>3.4</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="34">
         <v>3.79</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="34">
         <v>5.72</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="34">
         <v>4.9</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="34">
         <v>2.83</v>
       </c>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
+      <c r="A43" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" s="34">
         <v>15.53</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="34">
         <v>24.1</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="34">
         <v>20.17</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="34">
         <v>42.64</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="34">
         <v>57.18</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="34">
         <v>30.1</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="34">
         <v>20.11</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="34">
         <v>18.52</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="34">
         <v>21.25</v>
       </c>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" s="34">
         <v>26.01</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="34">
         <v>26.3</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="34">
         <v>24.98</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="34">
         <v>37.38</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="34">
         <v>34.61</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="34">
         <v>28.87</v>
       </c>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
+      <c r="A46" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B47" s="32">
+      <c r="A47" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="34">
         <v>4.42</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="34">
         <v>8.4</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="34">
         <v>9.95</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="34">
         <v>22.96</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="34">
         <v>32.54</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="34">
         <v>20.11</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="34">
         <v>11.64</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="34">
         <v>10.69</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="34">
         <v>8.42</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="34">
         <v>16.33</v>
       </c>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="34">
         <v>11.46</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="34">
         <v>13.53</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="34">
         <v>13.97</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="34">
         <v>21.8</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="34">
         <v>20.12</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="34">
         <v>14.34</v>
       </c>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
+      <c r="A49" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" s="34">
         <v>20.36</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="34">
         <v>55.78</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="34">
         <v>22.94</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="34">
         <v>47.24</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="34">
         <v>67.86</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="34">
         <v>42.55</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="34">
         <v>21.03</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="34">
         <v>25.45</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="34">
         <v>16.1</v>
       </c>
-      <c r="K50" s="30">
+      <c r="K50" s="32">
         <v>426.31</v>
       </c>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="B51" s="32">
+      <c r="A51" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B51" s="34">
         <v>32.73</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="34">
         <v>33.65</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="34">
         <v>29.32</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="34">
         <v>44.97</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="34">
         <v>41.25</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="34">
         <v>30.57</v>
       </c>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
+      <c r="A52" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="B53" s="32">
+      <c r="A53" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B53" s="34">
         <v>16.6</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="34">
         <v>22.48</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="34">
         <v>20.02</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="34">
         <v>41.52</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="34">
         <v>67.86</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="34">
         <v>42.55</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="34">
         <v>21.03</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="34">
         <v>25.3</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="34">
         <v>16.1</v>
       </c>
-      <c r="K53" s="30">
+      <c r="K53" s="32">
         <v>426.31</v>
       </c>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="B54" s="32">
+      <c r="A54" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B54" s="34">
         <v>5.67</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="34">
         <v>6.88</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="34">
         <v>7.7</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="34">
         <v>12.61</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="34">
         <v>12.09</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="34">
         <v>7.85</v>
       </c>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
+      <c r="A55" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" s="34">
         <v>0.26</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="37">
         <v>-0.77</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="34">
         <v>3.2</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="34">
         <v>4.04</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="34">
         <v>2.63</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="34">
         <v>2.54</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="34">
         <v>0.25</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="34">
         <v>1.7</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="33">
         <v>0.0</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="34">
         <v>4.18</v>
       </c>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B57" s="35">
+      <c r="A57" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B57" s="37">
         <v>-6.05</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="37">
         <v>-2.55</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="34">
         <v>1.1</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="34">
         <v>1.59</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="34">
         <v>0.26</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="34">
         <v>0.17</v>
       </c>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
+      <c r="A58" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B59" s="32">
+      <c r="A59" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B59" s="34">
         <v>1.68</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="34">
         <v>2.17</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="34">
         <v>3.21</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="34">
         <v>6.66</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="34">
         <v>10.43</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="34">
         <v>5.91</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="34">
         <v>3.04</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="34">
         <v>2.48</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="34">
         <v>1.76</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="34">
         <v>1.58</v>
       </c>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B60" s="32">
+      <c r="A60" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B60" s="34">
         <v>4.08</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="34">
         <v>5.04</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="34">
         <v>5.74</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="34">
         <v>6.16</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="34">
         <v>5.34</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="34">
         <v>3.26</v>
       </c>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
+      <c r="A61" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B62" s="34">
         <v>6.09</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="34">
         <v>8.29</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="34">
         <v>10.12</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="34">
         <v>19.95</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="34">
         <v>29.21</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="34">
         <v>18.32</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="34">
         <v>11.03</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="34">
         <v>10.79</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="34">
         <v>9.52</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="34">
         <v>16.19</v>
       </c>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
+      <c r="L62" s="33"/>
+      <c r="M62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B63" s="34">
         <v>13.57</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="34">
         <v>16.18</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="34">
         <v>17.75</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="34">
         <v>19.71</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="34">
         <v>18.65</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="34">
         <v>13.74</v>
       </c>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
-      <c r="M63" s="31"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>288</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
+      <c r="A64" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B65" s="34">
         <v>8.67</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="34">
         <v>10.47</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="34">
         <v>12.38</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="34">
         <v>22.4</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="34">
         <v>30.21</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="34">
         <v>19.63</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="34">
         <v>12.84</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="34">
         <v>11.12</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="34">
         <v>10.34</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="34">
         <v>29.78</v>
       </c>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="B66" s="34">
         <v>16.51</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="34">
         <v>18.62</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="34">
         <v>19.98</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="34">
         <v>21.38</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="34">
         <v>19.97</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="34">
         <v>15.36</v>
       </c>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
+      <c r="A67" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68" s="34">
         <v>26.5</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="34">
         <v>33.98</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="34">
         <v>24.42</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="34">
         <v>46.1</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="34">
         <v>59.76</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="34">
         <v>31.82</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="34">
         <v>22.31</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="34">
         <v>21.99</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="34">
         <v>29.53</v>
       </c>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" s="34">
         <v>38.74</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="34">
         <v>39.16</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="34">
         <v>37.83</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="34">
         <v>40.17</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="34">
         <v>37.53</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="34">
         <v>32.73</v>
       </c>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
